--- a/xlsx/packagedata template-alt2.xlsx
+++ b/xlsx/packagedata template-alt2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Collection\ReactThreejsFiber\Containerloadingsys\public\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8E59FA6-38D1-41D4-8D48-4DBDD2FB2EF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3629C03-B1B6-496F-B211-E7E1526917E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="22620" windowHeight="13500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="18">
   <si>
     <t>双向可叉</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -101,31 +101,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>LSA443</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>是否堆叠</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>否</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>单向可叉</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Wooden pallet</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>LSA463</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>LSA442</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -492,7 +468,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:N5"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.83203125" bestFit="1" customWidth="1"/>
@@ -548,7 +524,7 @@
         <v>10</v>
       </c>
       <c r="N1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
@@ -565,7 +541,7 @@
         <v>74</v>
       </c>
       <c r="E2">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="F2">
         <v>114.3</v>
@@ -574,7 +550,7 @@
         <v>16</v>
       </c>
       <c r="H2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I2" t="s">
         <v>15</v>
@@ -593,138 +569,6 @@
       </c>
       <c r="N2" t="s">
         <v>14</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A3">
-        <v>154143</v>
-      </c>
-      <c r="B3">
-        <v>125</v>
-      </c>
-      <c r="C3">
-        <v>80</v>
-      </c>
-      <c r="D3">
-        <v>100</v>
-      </c>
-      <c r="E3">
-        <v>30</v>
-      </c>
-      <c r="F3">
-        <v>427.3</v>
-      </c>
-      <c r="G3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H3">
-        <v>2</v>
-      </c>
-      <c r="I3" t="s">
-        <v>15</v>
-      </c>
-      <c r="J3" t="s">
-        <v>0</v>
-      </c>
-      <c r="K3" t="s">
-        <v>14</v>
-      </c>
-      <c r="L3">
-        <v>4</v>
-      </c>
-      <c r="M3" t="s">
-        <v>14</v>
-      </c>
-      <c r="N3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A4">
-        <v>154144</v>
-      </c>
-      <c r="B4">
-        <v>125</v>
-      </c>
-      <c r="C4">
-        <v>80</v>
-      </c>
-      <c r="D4">
-        <v>100</v>
-      </c>
-      <c r="E4">
-        <v>20</v>
-      </c>
-      <c r="F4">
-        <v>787.6</v>
-      </c>
-      <c r="G4" t="s">
-        <v>17</v>
-      </c>
-      <c r="H4">
-        <v>2</v>
-      </c>
-      <c r="I4" t="s">
-        <v>15</v>
-      </c>
-      <c r="J4" t="s">
-        <v>0</v>
-      </c>
-      <c r="K4" t="s">
-        <v>14</v>
-      </c>
-      <c r="L4">
-        <v>1</v>
-      </c>
-      <c r="M4" t="s">
-        <v>14</v>
-      </c>
-      <c r="N4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A5">
-        <v>154145</v>
-      </c>
-      <c r="B5">
-        <v>140</v>
-      </c>
-      <c r="C5">
-        <v>90</v>
-      </c>
-      <c r="D5">
-        <v>130</v>
-      </c>
-      <c r="E5">
-        <v>5</v>
-      </c>
-      <c r="F5">
-        <v>114.3</v>
-      </c>
-      <c r="G5" t="s">
-        <v>22</v>
-      </c>
-      <c r="H5">
-        <v>1</v>
-      </c>
-      <c r="I5" t="s">
-        <v>21</v>
-      </c>
-      <c r="J5" t="s">
-        <v>20</v>
-      </c>
-      <c r="K5" t="s">
-        <v>14</v>
-      </c>
-      <c r="L5">
-        <v>15</v>
-      </c>
-      <c r="M5" t="s">
-        <v>19</v>
-      </c>
-      <c r="N5" t="s">
-        <v>19</v>
       </c>
     </row>
   </sheetData>

--- a/xlsx/packagedata template-alt2.xlsx
+++ b/xlsx/packagedata template-alt2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Collection\ReactThreejsFiber\Containerloadingsys\public\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3629C03-B1B6-496F-B211-E7E1526917E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6313E1E-1DFD-4FC0-91B9-158A02C80098}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="22620" windowHeight="13500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -541,7 +541,7 @@
         <v>74</v>
       </c>
       <c r="E2">
-        <v>96</v>
+        <v>130</v>
       </c>
       <c r="F2">
         <v>114.3</v>
@@ -550,7 +550,7 @@
         <v>16</v>
       </c>
       <c r="H2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I2" t="s">
         <v>15</v>
